--- a/data/trans_dic/P39A1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,53; 75,98</t>
+          <t>67,98; 76,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,65; 75,86</t>
+          <t>69,58; 75,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,02; 74,77</t>
+          <t>70,03; 74,89</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,9; 82,65</t>
+          <t>70,87; 83,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,37; 76,7</t>
+          <t>62,13; 77,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,4; 77,2</t>
+          <t>67,21; 77,49</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,82; 72,14</t>
+          <t>63,54; 72,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,64; 68,66</t>
+          <t>62,6; 69,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,47; 69,7</t>
+          <t>64,34; 69,87</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 80,05</t>
+          <t>70,41; 79,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,93; 74,67</t>
+          <t>64,55; 74,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,25; 75,43</t>
+          <t>68,57; 75,33</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>288944; 320357</t>
+          <t>286628; 321028</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>420682; 458139</t>
+          <t>420202; 456031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>718074; 766807</t>
+          <t>718171; 768075</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1525525; 1778478</t>
+          <t>1524839; 1788355</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1287097; 1582755</t>
+          <t>1282063; 1602523</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2841057; 3254014</t>
+          <t>2833006; 3266553</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>393849; 445208</t>
+          <t>392132; 445519</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>395858; 433918</t>
+          <t>395639; 436807</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>805232; 870581</t>
+          <t>803693; 872709</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2243647; 2554005</t>
+          <t>2246458; 2520997</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2142231; 2463827</t>
+          <t>2129738; 2458636</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4429450; 4895398</t>
+          <t>4450418; 4888603</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A1_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,98; 76,14</t>
+          <t>67,96; 75,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,58; 75,51</t>
+          <t>71,02; 76,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,03; 74,89</t>
+          <t>70,73; 75,34</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>69,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,87; 83,11</t>
+          <t>68,76; 73,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,13; 77,66</t>
+          <t>65,26; 69,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,21; 77,49</t>
+          <t>67,78; 70,8</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,54; 72,19</t>
+          <t>65,42; 72,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,6; 69,12</t>
+          <t>62,31; 68,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,34; 69,87</t>
+          <t>64,89; 69,73</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,41; 79,02</t>
+          <t>69,18; 72,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,55; 74,52</t>
+          <t>66,74; 69,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,57; 75,33</t>
+          <t>68,4; 70,74</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>305072</t>
+          <t>333822</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>440198</t>
+          <t>484197</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>745269</t>
+          <t>818020</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>286628; 321028</t>
+          <t>315260; 351405</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>420202; 456031</t>
+          <t>466271; 500449</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>718171; 768075</t>
+          <t>792505; 844192</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1610993</t>
+          <t>1467296</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1411823</t>
+          <t>1347056</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3022816</t>
+          <t>2814352</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1524839; 1788355</t>
+          <t>1416126; 1511054</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1282063; 1602523</t>
+          <t>1307463; 1382917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2833006; 3266553</t>
+          <t>2754050; 2876833</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>422420</t>
+          <t>468837</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>416405</t>
+          <t>458545</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>838825</t>
+          <t>927382</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>392132; 445519</t>
+          <t>443225; 494054</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>395639; 436807</t>
+          <t>436241; 481623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>803693; 872709</t>
+          <t>893911; 960559</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2338485</t>
+          <t>2269955</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2268426</t>
+          <t>2289798</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4606910</t>
+          <t>4559753</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2246458; 2520997</t>
+          <t>2214436; 2326513</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2129738; 2458636</t>
+          <t>2242488; 2339035</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4450418; 4888603</t>
+          <t>4487955; 4641336</t>
         </is>
       </c>
     </row>
